--- a/jogos_2025-06-17.xlsx
+++ b/jogos_2025-06-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -193,6 +193,12 @@
     <t>12:00</t>
   </si>
   <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -205,12 +211,12 @@
     <t>China Chinese Super League</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Chile Primera División</t>
   </si>
   <si>
@@ -223,88 +229,130 @@
     <t>2024/2025</t>
   </si>
   <si>
+    <t>FC Seoul</t>
+  </si>
+  <si>
+    <t>Jeonbuk Motors</t>
+  </si>
+  <si>
     <t>Daegu</t>
   </si>
   <si>
-    <t>Jeonbuk Motors</t>
-  </si>
-  <si>
-    <t>FC Seoul</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>CR Belouizdad</t>
+  </si>
+  <si>
+    <t>ES Mostaganem</t>
+  </si>
+  <si>
     <t>ASO Chlef</t>
   </si>
   <si>
+    <t>NC Magra</t>
+  </si>
+  <si>
     <t>El Bayadh</t>
   </si>
   <si>
-    <t>Kuressaare</t>
-  </si>
-  <si>
     <t>JS Saoura</t>
   </si>
   <si>
-    <t>NC Magra</t>
-  </si>
-  <si>
-    <t>CR Belouizdad</t>
-  </si>
-  <si>
-    <t>ES Mostaganem</t>
-  </si>
-  <si>
     <t>Colo-Colo</t>
   </si>
   <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Gangwon</t>
+  </si>
+  <si>
+    <t>Suwon</t>
+  </si>
+  <si>
     <t>Pohang Steelers</t>
   </si>
   <si>
-    <t>Suwon</t>
-  </si>
-  <si>
-    <t>Gangwon</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
+    <t>Tammeka</t>
+  </si>
+  <si>
+    <t>MC Oran</t>
+  </si>
+  <si>
+    <t>JS Kabylie</t>
+  </si>
+  <si>
     <t>MC Alger</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>Oued Akbou</t>
   </si>
   <si>
-    <t>Tammeka</t>
-  </si>
-  <si>
     <t>Paradou AC</t>
   </si>
   <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>MC Oran</t>
-  </si>
-  <si>
-    <t>JS Kabylie</t>
-  </si>
-  <si>
     <t>Cobresal</t>
   </si>
   <si>
     <t>Avaí</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['72']</t>
+  </si>
+  <si>
+    <t>['52', '72']</t>
+  </si>
+  <si>
+    <t>['83']</t>
+  </si>
+  <si>
+    <t>['-1']</t>
+  </si>
+  <si>
+    <t>['31', '8']</t>
+  </si>
+  <si>
+    <t>['45+1', '58']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['7', '17']</t>
+  </si>
+  <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['5', '31']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
+    <t>['45', '38', '90+8']</t>
+  </si>
+  <si>
+    <t>['66']</t>
+  </si>
+  <si>
+    <t>['38']</t>
   </si>
 </sst>
 </file>
@@ -849,151 +897,151 @@
         <v>56</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L2">
-        <v>3.53</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
-        <v>3.25</v>
+        <v>3.32</v>
       </c>
       <c r="N2">
-        <v>1.89</v>
+        <v>5.2</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R2">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T2">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="V2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AB2">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AC2">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AJ2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AK2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP2">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AU2">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AW2">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AX2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY2">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ2">
         <v>0</v>
@@ -1002,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="BB2">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BC2">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BD2" s="3">
         <v>45825.3125</v>
@@ -1019,31 +1067,31 @@
         <v>56</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L3">
         <v>1.6</v>
@@ -1058,7 +1106,7 @@
         <v>1.44</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1082,16 +1130,16 @@
         <v>1.1</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AB3">
         <v>1.87</v>
@@ -1100,10 +1148,10 @@
         <v>1.83</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF3">
         <v>1.83</v>
@@ -1112,58 +1160,58 @@
         <v>1.83</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AJ3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="AK3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU3">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ3">
         <v>0</v>
@@ -1189,151 +1237,151 @@
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L4">
-        <v>1.6</v>
+        <v>3.53</v>
       </c>
       <c r="M4">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N4">
-        <v>5.2</v>
+        <v>1.89</v>
       </c>
       <c r="O4">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="P4">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q4">
+        <v>1.57</v>
+      </c>
+      <c r="R4">
+        <v>1.36</v>
+      </c>
+      <c r="S4">
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <v>2.63</v>
+      </c>
+      <c r="U4">
+        <v>1.44</v>
+      </c>
+      <c r="V4">
+        <v>7</v>
+      </c>
+      <c r="W4">
+        <v>1.1</v>
+      </c>
+      <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>9.5</v>
+      </c>
+      <c r="Z4">
+        <v>1.28</v>
+      </c>
+      <c r="AA4">
+        <v>3.55</v>
+      </c>
+      <c r="AB4">
+        <v>1.86</v>
+      </c>
+      <c r="AC4">
+        <v>1.84</v>
+      </c>
+      <c r="AD4">
         <v>3.1</v>
       </c>
-      <c r="R4">
-        <v>1.48</v>
-      </c>
-      <c r="S4">
-        <v>2.5</v>
-      </c>
-      <c r="T4">
-        <v>3.2</v>
-      </c>
-      <c r="U4">
-        <v>1.3</v>
-      </c>
-      <c r="V4">
-        <v>7.8</v>
-      </c>
-      <c r="W4">
-        <v>1.02</v>
-      </c>
-      <c r="X4">
-        <v>1.08</v>
-      </c>
-      <c r="Y4">
-        <v>7.5</v>
-      </c>
-      <c r="Z4">
-        <v>1.42</v>
-      </c>
-      <c r="AA4">
-        <v>2.8</v>
-      </c>
-      <c r="AB4">
-        <v>2.1</v>
-      </c>
-      <c r="AC4">
-        <v>1.6</v>
-      </c>
-      <c r="AD4">
-        <v>4.2</v>
-      </c>
       <c r="AE4">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AF4">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AG4">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AI4">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ4" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="AL4">
-        <v>1.14</v>
+        <v>1.77</v>
       </c>
       <c r="AM4">
         <v>1.25</v>
       </c>
       <c r="AN4">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP4">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AQ4">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AR4">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AS4">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="AT4">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="AU4">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AV4">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AW4">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AX4">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AY4">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AZ4">
         <v>0</v>
@@ -1342,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="BB4">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="BC4">
-        <v>3.1</v>
+        <v>1.57</v>
       </c>
       <c r="BD4" s="3">
         <v>45825.3125</v>
@@ -1359,19 +1407,19 @@
         <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1383,16 +1431,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="N5">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="O5">
         <v>1.42</v>
@@ -1434,16 +1482,16 @@
         <v>4.75</v>
       </c>
       <c r="AB5">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AC5">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD5">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AE5">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
@@ -1458,10 +1506,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="AK5" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL5">
         <v>1.08</v>
@@ -1473,7 +1521,7 @@
         <v>2.7</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP5">
         <v>1.26</v>
@@ -1529,121 +1577,121 @@
         <v>58</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L6">
+        <v>2.1</v>
+      </c>
+      <c r="M6">
+        <v>3.5</v>
+      </c>
+      <c r="N6">
+        <v>2.75</v>
+      </c>
+      <c r="O6">
+        <v>1.67</v>
+      </c>
+      <c r="P6">
+        <v>10</v>
+      </c>
+      <c r="Q6">
+        <v>2.3</v>
+      </c>
+      <c r="R6">
+        <v>1.2</v>
+      </c>
+      <c r="S6">
+        <v>3.8</v>
+      </c>
+      <c r="T6">
+        <v>2.19</v>
+      </c>
+      <c r="U6">
+        <v>1.65</v>
+      </c>
+      <c r="V6">
         <v>4.1</v>
       </c>
-      <c r="M6">
-        <v>2.88</v>
-      </c>
-      <c r="N6">
-        <v>1.97</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <v>0</v>
-      </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AJ6" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AP6">
         <v>0</v>
@@ -1682,10 +1730,10 @@
         <v>0</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD6" s="3">
         <v>45825.5</v>
@@ -1696,43 +1744,43 @@
         <v>45825</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1774,10 +1822,10 @@
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1798,10 +1846,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1813,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -1858,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="BD7" s="3">
-        <v>45825.5</v>
+        <v>45825.5625</v>
       </c>
     </row>
     <row r="8" spans="1:56">
@@ -1866,19 +1914,19 @@
         <v>45825</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1893,16 +1941,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1938,16 +1986,16 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1968,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK8" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1983,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP8">
         <v>0</v>
@@ -2028,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="BD8" s="3">
-        <v>45825.5</v>
+        <v>45825.5625</v>
       </c>
     </row>
     <row r="9" spans="1:56">
@@ -2036,19 +2084,19 @@
         <v>45825</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2063,16 +2111,16 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2108,16 +2156,16 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2138,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK9" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2153,7 +2201,7 @@
         <v>0</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP9">
         <v>0</v>
@@ -2198,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="BD9" s="3">
-        <v>45825.5</v>
+        <v>45825.5625</v>
       </c>
     </row>
     <row r="10" spans="1:56">
@@ -2206,43 +2254,43 @@
         <v>45825</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L10">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="M10">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N10">
-        <v>5.17</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -2278,16 +2326,16 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB10">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AC10">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -2308,10 +2356,10 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="AK10" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2323,7 +2371,7 @@
         <v>0</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AP10">
         <v>0</v>
@@ -2368,7 +2416,7 @@
         <v>0</v>
       </c>
       <c r="BD10" s="3">
-        <v>45825.5</v>
+        <v>45825.5625</v>
       </c>
     </row>
     <row r="11" spans="1:56">
@@ -2376,43 +2424,43 @@
         <v>45825</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>2.06</v>
       </c>
       <c r="M11">
-        <v>4.7</v>
+        <v>2.88</v>
       </c>
       <c r="N11">
-        <v>12.1</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2448,16 +2496,16 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2478,10 +2526,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK11" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2493,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP11">
         <v>0</v>
@@ -2538,7 +2586,7 @@
         <v>0</v>
       </c>
       <c r="BD11" s="3">
-        <v>45825.5</v>
+        <v>45825.5625</v>
       </c>
     </row>
     <row r="12" spans="1:56">
@@ -2546,19 +2594,19 @@
         <v>45825</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2573,16 +2621,16 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L12">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="M12">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="N12">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="O12">
         <v>0</v>
@@ -2624,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD12">
         <v>0</v>
@@ -2648,10 +2696,10 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK12" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2708,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="BD12" s="3">
-        <v>45825.5</v>
+        <v>45825.66666666666</v>
       </c>
     </row>
     <row r="13" spans="1:56">
@@ -2716,19 +2764,19 @@
         <v>45825</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2743,7 +2791,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L13">
         <v>1.45</v>
@@ -2818,10 +2866,10 @@
         <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK13" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL13">
         <v>1.08</v>
@@ -2886,19 +2934,19 @@
         <v>45825</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2913,16 +2961,16 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L14">
-        <v>2.89</v>
+        <v>2.31</v>
       </c>
       <c r="M14">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="N14">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="O14">
         <v>1.83</v>
@@ -2934,52 +2982,52 @@
         <v>2.4</v>
       </c>
       <c r="R14">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="S14">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="T14">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="U14">
         <v>1.25</v>
       </c>
       <c r="V14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="Y14">
         <v>6</v>
       </c>
       <c r="Z14">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AA14">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AB14">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AC14">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AD14">
-        <v>5.05</v>
+        <v>4.4</v>
       </c>
       <c r="AE14">
         <v>1.14</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG14">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH14">
         <v>10</v>
@@ -2988,10 +3036,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ14" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AK14" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="AL14">
         <v>1.4</v>
@@ -3000,40 +3048,40 @@
         <v>1.37</v>
       </c>
       <c r="AN14">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AO14">
         <v>-1</v>
       </c>
       <c r="AP14">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AR14">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AS14">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AT14">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="AU14">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AV14">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="AW14">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AX14">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AY14">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AZ14">
         <v>0</v>

--- a/jogos_2025-06-17.xlsx
+++ b/jogos_2025-06-17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="99">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -229,36 +175,36 @@
     <t>2024/2025</t>
   </si>
   <si>
+    <t>Daegu</t>
+  </si>
+  <si>
     <t>FC Seoul</t>
   </si>
   <si>
     <t>Jeonbuk Motors</t>
   </si>
   <si>
-    <t>Daegu</t>
-  </si>
-  <si>
     <t>Beijing Guoan</t>
   </si>
   <si>
     <t>Kuressaare</t>
   </si>
   <si>
+    <t>El Bayadh</t>
+  </si>
+  <si>
+    <t>ASO Chlef</t>
+  </si>
+  <si>
     <t>CR Belouizdad</t>
   </si>
   <si>
+    <t>NC Magra</t>
+  </si>
+  <si>
     <t>ES Mostaganem</t>
   </si>
   <si>
-    <t>ASO Chlef</t>
-  </si>
-  <si>
-    <t>NC Magra</t>
-  </si>
-  <si>
-    <t>El Bayadh</t>
-  </si>
-  <si>
     <t>JS Saoura</t>
   </si>
   <si>
@@ -268,36 +214,36 @@
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>Pohang Steelers</t>
+  </si>
+  <si>
     <t>Gangwon</t>
   </si>
   <si>
     <t>Suwon</t>
   </si>
   <si>
-    <t>Pohang Steelers</t>
-  </si>
-  <si>
     <t>Qingdao Youth Island</t>
   </si>
   <si>
     <t>Tammeka</t>
   </si>
   <si>
+    <t>Oued Akbou</t>
+  </si>
+  <si>
+    <t>MC Alger</t>
+  </si>
+  <si>
     <t>MC Oran</t>
   </si>
   <si>
+    <t>CS Constantine</t>
+  </si>
+  <si>
     <t>JS Kabylie</t>
   </si>
   <si>
-    <t>MC Alger</t>
-  </si>
-  <si>
-    <t>CS Constantine</t>
-  </si>
-  <si>
-    <t>Oued Akbou</t>
-  </si>
-  <si>
     <t>Paradou AC</t>
   </si>
   <si>
@@ -310,7 +256,7 @@
     <t>complete</t>
   </si>
   <si>
-    <t>incomplete</t>
+    <t>['83']</t>
   </si>
   <si>
     <t>['72']</t>
@@ -319,40 +265,52 @@
     <t>['52', '72']</t>
   </si>
   <si>
-    <t>['83']</t>
-  </si>
-  <si>
     <t>['-1']</t>
   </si>
   <si>
     <t>['31', '8']</t>
   </si>
   <si>
+    <t>[]</t>
+  </si>
+  <si>
     <t>['45+1', '58']</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
     <t>['7', '17']</t>
   </si>
   <si>
+    <t>['52', '64', '90+3']</t>
+  </si>
+  <si>
+    <t>['27', '55', '75', '85']</t>
+  </si>
+  <si>
+    <t>['52']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['25']</t>
   </si>
   <si>
     <t>['5', '31']</t>
   </si>
   <si>
-    <t>['32']</t>
-  </si>
-  <si>
     <t>['45', '38', '90+8']</t>
   </si>
   <si>
+    <t>['38']</t>
+  </si>
+  <si>
     <t>['66']</t>
   </si>
   <si>
-    <t>['38']</t>
+    <t>['45+6', '87']</t>
+  </si>
+  <si>
+    <t>['28']</t>
   </si>
 </sst>
 </file>
@@ -716,10 +674,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD14"/>
+  <dimension ref="A1:AL14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,79 +792,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45825</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -921,365 +825,257 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>3.53</v>
       </c>
       <c r="M2">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="N2">
-        <v>5.2</v>
+        <v>1.89</v>
       </c>
       <c r="O2">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="P2">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q2">
+        <v>1.57</v>
+      </c>
+      <c r="R2">
+        <v>1.36</v>
+      </c>
+      <c r="S2">
+        <v>3</v>
+      </c>
+      <c r="T2">
+        <v>2.63</v>
+      </c>
+      <c r="U2">
+        <v>1.44</v>
+      </c>
+      <c r="V2">
+        <v>7</v>
+      </c>
+      <c r="W2">
+        <v>1.1</v>
+      </c>
+      <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>9.5</v>
+      </c>
+      <c r="Z2">
+        <v>1.28</v>
+      </c>
+      <c r="AA2">
+        <v>3.55</v>
+      </c>
+      <c r="AB2">
+        <v>1.86</v>
+      </c>
+      <c r="AC2">
+        <v>1.84</v>
+      </c>
+      <c r="AD2">
         <v>3.1</v>
       </c>
-      <c r="R2">
-        <v>1.48</v>
-      </c>
-      <c r="S2">
-        <v>2.5</v>
-      </c>
-      <c r="T2">
-        <v>3.2</v>
-      </c>
-      <c r="U2">
-        <v>1.3</v>
-      </c>
-      <c r="V2">
-        <v>7.8</v>
-      </c>
-      <c r="W2">
-        <v>1.02</v>
-      </c>
-      <c r="X2">
-        <v>1.08</v>
-      </c>
-      <c r="Y2">
-        <v>7.5</v>
-      </c>
-      <c r="Z2">
-        <v>1.42</v>
-      </c>
-      <c r="AA2">
-        <v>2.8</v>
-      </c>
-      <c r="AB2">
+      <c r="AE2">
+        <v>1.35</v>
+      </c>
+      <c r="AF2">
+        <v>1.73</v>
+      </c>
+      <c r="AG2">
         <v>2</v>
       </c>
-      <c r="AC2">
-        <v>1.72</v>
-      </c>
-      <c r="AD2">
-        <v>4.2</v>
-      </c>
-      <c r="AE2">
-        <v>1.22</v>
-      </c>
-      <c r="AF2">
-        <v>2.1</v>
-      </c>
-      <c r="AG2">
-        <v>1.62</v>
-      </c>
       <c r="AH2">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="AI2">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AJ2" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="s">
-        <v>107</v>
-      </c>
-      <c r="AL2">
-        <v>1.14</v>
-      </c>
-      <c r="AM2">
-        <v>1.25</v>
-      </c>
-      <c r="AN2">
-        <v>2.15</v>
-      </c>
-      <c r="AO2">
-        <v>8</v>
-      </c>
-      <c r="AP2">
-        <v>1.47</v>
-      </c>
-      <c r="AQ2">
-        <v>1.78</v>
-      </c>
-      <c r="AR2">
-        <v>2.23</v>
-      </c>
-      <c r="AS2">
-        <v>2.9</v>
-      </c>
-      <c r="AT2">
-        <v>3.9</v>
-      </c>
-      <c r="AU2">
-        <v>2.48</v>
-      </c>
-      <c r="AV2">
-        <v>1.91</v>
-      </c>
-      <c r="AW2">
-        <v>1.56</v>
-      </c>
-      <c r="AX2">
-        <v>1.34</v>
-      </c>
-      <c r="AY2">
-        <v>1.21</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.55</v>
-      </c>
-      <c r="BC2">
-        <v>3.1</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>91</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45825.3125</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45825</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L3">
         <v>1.6</v>
       </c>
       <c r="M3">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="P3">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
       </c>
       <c r="R3">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V3">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Z3">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AA3">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="AB3">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC3">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AD3">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AE3">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AF3">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AH3">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="AI3">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AJ3" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK3" t="s">
-        <v>108</v>
-      </c>
-      <c r="AL3">
-        <v>1.15</v>
-      </c>
-      <c r="AM3">
-        <v>1.2</v>
-      </c>
-      <c r="AN3">
-        <v>2.2</v>
-      </c>
-      <c r="AO3">
-        <v>9</v>
-      </c>
-      <c r="AP3">
-        <v>1.45</v>
-      </c>
-      <c r="AQ3">
-        <v>1.74</v>
-      </c>
-      <c r="AR3">
-        <v>2.18</v>
-      </c>
-      <c r="AS3">
-        <v>2.8</v>
-      </c>
-      <c r="AT3">
-        <v>3.8</v>
-      </c>
-      <c r="AU3">
-        <v>2.55</v>
-      </c>
-      <c r="AV3">
-        <v>1.95</v>
-      </c>
-      <c r="AW3">
-        <v>1.58</v>
-      </c>
-      <c r="AX3">
-        <v>1.36</v>
-      </c>
-      <c r="AY3">
-        <v>1.22</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.44</v>
-      </c>
-      <c r="BC3">
-        <v>3.1</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>92</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45825.3125</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45825</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L4">
-        <v>3.53</v>
+        <v>1.6</v>
       </c>
       <c r="M4">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N4">
-        <v>1.89</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>1.57</v>
+        <v>3.1</v>
       </c>
       <c r="R4">
         <v>1.36</v>
@@ -1288,10 +1084,10 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1303,120 +1099,66 @@
         <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AA4">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AB4">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AC4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD4">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AE4">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AF4">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH4">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AI4">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="AK4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL4">
-        <v>1.77</v>
-      </c>
-      <c r="AM4">
-        <v>1.25</v>
-      </c>
-      <c r="AN4">
-        <v>1.28</v>
-      </c>
-      <c r="AO4">
-        <v>6</v>
-      </c>
-      <c r="AP4">
-        <v>1.4</v>
-      </c>
-      <c r="AQ4">
-        <v>1.67</v>
-      </c>
-      <c r="AR4">
-        <v>2.07</v>
-      </c>
-      <c r="AS4">
-        <v>2.65</v>
-      </c>
-      <c r="AT4">
-        <v>3.45</v>
-      </c>
-      <c r="AU4">
-        <v>2.7</v>
-      </c>
-      <c r="AV4">
-        <v>2.07</v>
-      </c>
-      <c r="AW4">
-        <v>1.68</v>
-      </c>
-      <c r="AX4">
-        <v>1.42</v>
-      </c>
-      <c r="AY4">
-        <v>1.25</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>2.5</v>
-      </c>
-      <c r="BC4">
-        <v>1.57</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>93</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45825.3125</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45825</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" t="s">
         <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F5" t="s">
-        <v>87</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1431,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L5">
         <v>1.32</v>
@@ -1506,87 +1248,33 @@
         <v>1.22</v>
       </c>
       <c r="AJ5" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="AK5" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL5">
-        <v>1.08</v>
-      </c>
-      <c r="AM5">
-        <v>1.14</v>
-      </c>
-      <c r="AN5">
-        <v>2.7</v>
-      </c>
-      <c r="AO5">
-        <v>12</v>
-      </c>
-      <c r="AP5">
-        <v>1.26</v>
-      </c>
-      <c r="AQ5">
-        <v>1.46</v>
-      </c>
-      <c r="AR5">
-        <v>1.72</v>
-      </c>
-      <c r="AS5">
-        <v>2.12</v>
-      </c>
-      <c r="AT5">
-        <v>2.65</v>
-      </c>
-      <c r="AU5">
-        <v>3.4</v>
-      </c>
-      <c r="AV5">
-        <v>2.5</v>
-      </c>
-      <c r="AW5">
-        <v>1.97</v>
-      </c>
-      <c r="AX5">
-        <v>1.63</v>
-      </c>
-      <c r="AY5">
-        <v>1.4</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.42</v>
-      </c>
-      <c r="BC5">
-        <v>3</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45825.35763888889</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45825</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1601,7 +1289,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L6">
         <v>2.1</v>
@@ -1676,156 +1364,102 @@
         <v>1.25</v>
       </c>
       <c r="AJ6" t="s">
-        <v>103</v>
+        <v>84</v>
       </c>
       <c r="AK6" t="s">
-        <v>110</v>
-      </c>
-      <c r="AL6">
-        <v>1.29</v>
-      </c>
-      <c r="AM6">
-        <v>1.25</v>
-      </c>
-      <c r="AN6">
-        <v>1.67</v>
-      </c>
-      <c r="AO6">
-        <v>19</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.67</v>
-      </c>
-      <c r="BC6">
-        <v>2.3</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>94</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45825.5</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45825</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7">
+        <v>2.06</v>
+      </c>
+      <c r="M7">
+        <v>2.88</v>
+      </c>
+      <c r="N7">
+        <v>3.9</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>1.67</v>
+      </c>
+      <c r="AA7">
         <v>2</v>
       </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="s">
-        <v>97</v>
-      </c>
-      <c r="L7">
-        <v>1.2</v>
-      </c>
-      <c r="M7">
-        <v>5.75</v>
-      </c>
-      <c r="N7">
-        <v>12</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
       <c r="AB7">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="AC7">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1846,87 +1480,33 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="AK7" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>9</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>95</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45825.5625</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45825</v>
       </c>
       <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" t="s">
         <v>59</v>
       </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1941,16 +1521,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L8">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>3.19</v>
+        <v>2.95</v>
       </c>
       <c r="N8">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1986,16 +1566,16 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AB8">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AC8">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -2016,111 +1596,57 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="AK8" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>0</v>
-      </c>
-      <c r="AO8">
-        <v>15</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>0</v>
-      </c>
-      <c r="BC8">
-        <v>0</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45825.5625</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45825</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L9">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="M9">
-        <v>2.95</v>
+        <v>5.75</v>
       </c>
       <c r="N9">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -2156,16 +1682,16 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC9">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="AD9">
         <v>0</v>
@@ -2186,87 +1712,33 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="AK9" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>0</v>
-      </c>
-      <c r="AO9">
-        <v>4</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>0</v>
-      </c>
-      <c r="BC9">
-        <v>0</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45825.5625</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45825</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2281,7 +1753,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L10">
         <v>1.53</v>
@@ -2356,111 +1828,57 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="AK10" t="s">
-        <v>111</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
-        <v>0</v>
-      </c>
-      <c r="AO10">
-        <v>6</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>0</v>
-      </c>
-      <c r="BC10">
-        <v>0</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>96</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45825.5625</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45825</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D11" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L11">
-        <v>2.06</v>
+        <v>3.05</v>
       </c>
       <c r="M11">
-        <v>2.88</v>
+        <v>3.19</v>
       </c>
       <c r="N11">
-        <v>3.9</v>
+        <v>2.2</v>
       </c>
       <c r="O11">
         <v>0</v>
@@ -2496,16 +1914,16 @@
         <v>0</v>
       </c>
       <c r="Z11">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="AB11">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="AC11">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -2526,102 +1944,48 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="AK11" t="s">
-        <v>112</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>8</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45825.5625</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45825</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="L12">
         <v>1.75</v>
@@ -2696,102 +2060,48 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="AK12" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AO12">
-        <v>-1</v>
-      </c>
-      <c r="AP12">
-        <v>0</v>
-      </c>
-      <c r="AQ12">
-        <v>0</v>
-      </c>
-      <c r="AR12">
-        <v>0</v>
-      </c>
-      <c r="AS12">
-        <v>0</v>
-      </c>
-      <c r="AT12">
-        <v>0</v>
-      </c>
-      <c r="AU12">
-        <v>0</v>
-      </c>
-      <c r="AV12">
-        <v>0</v>
-      </c>
-      <c r="AW12">
-        <v>0</v>
-      </c>
-      <c r="AX12">
-        <v>0</v>
-      </c>
-      <c r="AY12">
-        <v>0</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>0</v>
-      </c>
-      <c r="BC12">
-        <v>0</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>97</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45825.66666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45825</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="L13">
         <v>1.45</v>
@@ -2866,111 +2176,57 @@
         <v>1.09</v>
       </c>
       <c r="AJ13" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="AK13" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL13">
-        <v>1.08</v>
-      </c>
-      <c r="AM13">
-        <v>1.18</v>
-      </c>
-      <c r="AN13">
-        <v>2.78</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.28</v>
-      </c>
-      <c r="AQ13">
-        <v>1.49</v>
-      </c>
-      <c r="AR13">
-        <v>1.79</v>
-      </c>
-      <c r="AS13">
-        <v>2.23</v>
-      </c>
-      <c r="AT13">
-        <v>2.88</v>
-      </c>
-      <c r="AU13">
-        <v>3.15</v>
-      </c>
-      <c r="AV13">
-        <v>2.35</v>
-      </c>
-      <c r="AW13">
-        <v>1.85</v>
-      </c>
-      <c r="AX13">
-        <v>1.54</v>
-      </c>
-      <c r="AY13">
-        <v>1.33</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.3</v>
-      </c>
-      <c r="BC13">
-        <v>3.75</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>85</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45825.79166666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45825</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="L14">
         <v>2.31</v>
       </c>
       <c r="M14">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N14">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="O14">
         <v>1.83</v>
@@ -2982,52 +2238,52 @@
         <v>2.4</v>
       </c>
       <c r="R14">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S14">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="T14">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="U14">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="V14">
         <v>10</v>
       </c>
       <c r="W14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="Z14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AA14">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AB14">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="AC14">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AD14">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF14">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AG14">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AH14">
         <v>10</v>
@@ -3036,66 +2292,12 @@
         <v>1.04</v>
       </c>
       <c r="AJ14" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AL14">
-        <v>1.4</v>
-      </c>
-      <c r="AM14">
-        <v>1.37</v>
-      </c>
-      <c r="AN14">
-        <v>1.62</v>
-      </c>
-      <c r="AO14">
-        <v>-1</v>
-      </c>
-      <c r="AP14">
-        <v>1.18</v>
-      </c>
-      <c r="AQ14">
-        <v>1.38</v>
-      </c>
-      <c r="AR14">
-        <v>1.77</v>
-      </c>
-      <c r="AS14">
-        <v>1.96</v>
-      </c>
-      <c r="AT14">
-        <v>2.43</v>
-      </c>
-      <c r="AU14">
-        <v>4.05</v>
-      </c>
-      <c r="AV14">
-        <v>2.95</v>
-      </c>
-      <c r="AW14">
-        <v>2.25</v>
-      </c>
-      <c r="AX14">
-        <v>1.79</v>
-      </c>
-      <c r="AY14">
-        <v>1.49</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.83</v>
-      </c>
-      <c r="BC14">
-        <v>2.4</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>98</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45825.8125</v>
       </c>
     </row>

--- a/jogos_2025-06-17.xlsx
+++ b/jogos_2025-06-17.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Jeonbuk Motors</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -672,77 +672,77 @@
         <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.25</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.05</v>
-      </c>
       <c r="Q2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.3</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['72']</t>
+          <t>['52', '72']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['5', '31']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AJ2" t="n">
         <v>3.1</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jeonbuk Motors</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -801,77 +801,77 @@
         <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['52', '72']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['5', '31']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AJ3" t="n">
         <v>3.1</v>
@@ -1933,22 +1933,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.2</v>
+        <v>3.05</v>
       </c>
       <c r="M12" t="n">
-        <v>5.75</v>
+        <v>3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.85</v>
+        <v>2.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['45+1', '58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.05</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.19</v>
+        <v>5.75</v>
       </c>
       <c r="N13" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1', '58']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
